--- a/AtchisonRegime/Outputs/Japan/df_regCLI_Japan.xlsx
+++ b/AtchisonRegime/Outputs/Japan/df_regCLI_Japan.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H761"/>
+  <dimension ref="A1:H762"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19955,22 +19955,22 @@
         <v>45443</v>
       </c>
       <c r="B751" t="n">
-        <v>100.14</v>
+        <v>100.1349</v>
       </c>
       <c r="C751" t="n">
-        <v>100.1033333333333</v>
+        <v>100.1016333333333</v>
       </c>
       <c r="D751" t="n">
-        <v>100.2913888888889</v>
+        <v>100.2912472222222</v>
       </c>
       <c r="E751" t="n">
-        <v>0.2624625445690789</v>
+        <v>0.2625479553325349</v>
       </c>
       <c r="F751" t="b">
         <v>1</v>
       </c>
       <c r="G751" t="n">
-        <v>0.1143020237392588</v>
+        <v>0.09483981685732353</v>
       </c>
       <c r="H751" t="b">
         <v>1</v>
@@ -19981,22 +19981,22 @@
         <v>45473</v>
       </c>
       <c r="B752" t="n">
-        <v>100.16</v>
+        <v>100.1416</v>
       </c>
       <c r="C752" t="n">
-        <v>100.1366666666667</v>
+        <v>100.1288333333333</v>
       </c>
       <c r="D752" t="n">
-        <v>100.2772222222222</v>
+        <v>100.2765694444444</v>
       </c>
       <c r="E752" t="n">
-        <v>0.2551034648488114</v>
+        <v>0.255442747087822</v>
       </c>
       <c r="F752" t="b">
         <v>1</v>
       </c>
       <c r="G752" t="n">
-        <v>0.07839956235737192</v>
+        <v>0.02622896941243575</v>
       </c>
       <c r="H752" t="b">
         <v>1</v>
@@ -20007,22 +20007,22 @@
         <v>45504</v>
       </c>
       <c r="B753" t="n">
-        <v>100.15</v>
+        <v>100.1207</v>
       </c>
       <c r="C753" t="n">
-        <v>100.15</v>
+        <v>100.1324</v>
       </c>
       <c r="D753" t="n">
-        <v>100.2619444444444</v>
+        <v>100.2604777777778</v>
       </c>
       <c r="E753" t="n">
-        <v>0.245343135156351</v>
+        <v>0.2460815684875624</v>
       </c>
       <c r="F753" t="b">
         <v>0</v>
       </c>
       <c r="G753" t="n">
-        <v>-0.04075924110783925</v>
+        <v>-0.08493118817654892</v>
       </c>
       <c r="H753" t="b">
         <v>1</v>
@@ -20033,22 +20033,22 @@
         <v>45535</v>
       </c>
       <c r="B754" t="n">
-        <v>100.11</v>
+        <v>100.0774</v>
       </c>
       <c r="C754" t="n">
-        <v>100.14</v>
+        <v>100.1132333333333</v>
       </c>
       <c r="D754" t="n">
-        <v>100.2458333333333</v>
+        <v>100.2434611111111</v>
       </c>
       <c r="E754" t="n">
-        <v>0.2352673251554727</v>
+        <v>0.2365265654399635</v>
       </c>
       <c r="F754" t="b">
         <v>0</v>
       </c>
       <c r="G754" t="n">
-        <v>-0.1700193597796587</v>
+        <v>-0.1830661174124763</v>
       </c>
       <c r="H754" t="b">
         <v>1</v>
@@ -20059,22 +20059,22 @@
         <v>45565</v>
       </c>
       <c r="B755" t="n">
-        <v>100.06</v>
+        <v>100.0307</v>
       </c>
       <c r="C755" t="n">
-        <v>100.1066666666667</v>
+        <v>100.0762666666667</v>
       </c>
       <c r="D755" t="n">
-        <v>100.2291666666667</v>
+        <v>100.2259805555556</v>
       </c>
       <c r="E755" t="n">
-        <v>0.2261652366872815</v>
+        <v>0.2279618198854683</v>
       </c>
       <c r="F755" t="b">
         <v>0</v>
       </c>
       <c r="G755" t="n">
-        <v>-0.2210773005275436</v>
+        <v>-0.2048588663815025</v>
       </c>
       <c r="H755" t="b">
         <v>0</v>
@@ -20085,22 +20085,22 @@
         <v>45596</v>
       </c>
       <c r="B756" t="n">
-        <v>99.98999999999999</v>
+        <v>99.98074</v>
       </c>
       <c r="C756" t="n">
-        <v>100.0533333333333</v>
+        <v>100.0296133333333</v>
       </c>
       <c r="D756" t="n">
-        <v>100.2111111111111</v>
+        <v>100.2076677777778</v>
       </c>
       <c r="E756" t="n">
-        <v>0.2182368016339245</v>
+        <v>0.220096643982056</v>
       </c>
       <c r="F756" t="b">
         <v>0</v>
       </c>
       <c r="G756" t="n">
-        <v>-0.3207525013009814</v>
+        <v>-0.2269911939414751</v>
       </c>
       <c r="H756" t="b">
         <v>0</v>
@@ -20111,22 +20111,22 @@
         <v>45626</v>
       </c>
       <c r="B757" t="n">
-        <v>99.93000000000001</v>
+        <v>99.93494</v>
       </c>
       <c r="C757" t="n">
-        <v>99.99333333333334</v>
+        <v>99.98212666666666</v>
       </c>
       <c r="D757" t="n">
-        <v>100.1919444444444</v>
+        <v>100.1886383333333</v>
       </c>
       <c r="E757" t="n">
-        <v>0.2114956189274467</v>
+        <v>0.2129262053457959</v>
       </c>
       <c r="F757" t="b">
         <v>0</v>
       </c>
       <c r="G757" t="n">
-        <v>-0.2836938197787018</v>
+        <v>-0.2150979956911355</v>
       </c>
       <c r="H757" t="b">
         <v>0</v>
@@ -20137,22 +20137,22 @@
         <v>45657</v>
       </c>
       <c r="B758" t="n">
-        <v>99.87</v>
+        <v>99.90407999999999</v>
       </c>
       <c r="C758" t="n">
-        <v>99.92999999999999</v>
+        <v>99.93991999999999</v>
       </c>
       <c r="D758" t="n">
-        <v>100.1711111111111</v>
+        <v>100.1687516666667</v>
       </c>
       <c r="E758" t="n">
-        <v>0.2049637985847001</v>
+        <v>0.2047631529006621</v>
       </c>
       <c r="F758" t="b">
         <v>0</v>
       </c>
       <c r="G758" t="n">
-        <v>-0.2927346215005262</v>
+        <v>-0.150710709240619</v>
       </c>
       <c r="H758" t="b">
         <v>0</v>
@@ -20163,22 +20163,22 @@
         <v>45688</v>
       </c>
       <c r="B759" t="n">
-        <v>99.83</v>
+        <v>99.88742000000001</v>
       </c>
       <c r="C759" t="n">
-        <v>99.87666666666667</v>
+        <v>99.90881333333334</v>
       </c>
       <c r="D759" t="n">
-        <v>100.1491666666667</v>
+        <v>100.1484022222222</v>
       </c>
       <c r="E759" t="n">
-        <v>0.1976920404499325</v>
+        <v>0.1947960882436529</v>
       </c>
       <c r="F759" t="b">
         <v>0</v>
       </c>
       <c r="G759" t="n">
-        <v>-0.2023349038685079</v>
+        <v>-0.08552533138729648</v>
       </c>
       <c r="H759" t="b">
         <v>0</v>
@@ -20189,22 +20189,22 @@
         <v>45716</v>
       </c>
       <c r="B760" t="n">
-        <v>99.8</v>
+        <v>99.87298</v>
       </c>
       <c r="C760" t="n">
-        <v>99.83333333333333</v>
+        <v>99.88816000000001</v>
       </c>
       <c r="D760" t="n">
-        <v>100.1269444444444</v>
+        <v>100.1282072222222</v>
       </c>
       <c r="E760" t="n">
-        <v>0.1903953697586051</v>
+        <v>0.1840285489130201</v>
       </c>
       <c r="F760" t="b">
         <v>0</v>
       </c>
       <c r="G760" t="n">
-        <v>-0.1575668569988701</v>
+        <v>-0.07846608629638509</v>
       </c>
       <c r="H760" t="b">
         <v>0</v>
@@ -20215,24 +20215,50 @@
         <v>45747</v>
       </c>
       <c r="B761" t="n">
-        <v>99.78</v>
+        <v>99.85392</v>
       </c>
       <c r="C761" t="n">
-        <v>99.80333333333333</v>
+        <v>99.87144000000001</v>
       </c>
       <c r="D761" t="n">
-        <v>100.105</v>
+        <v>100.1083161111111</v>
       </c>
       <c r="E761" t="n">
-        <v>0.183264056175338</v>
+        <v>0.173298811590975</v>
       </c>
       <c r="F761" t="b">
         <v>0</v>
       </c>
       <c r="G761" t="n">
-        <v>-0.1091321474455471</v>
+        <v>-0.1099834431928019</v>
       </c>
       <c r="H761" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" s="2" t="n">
+        <v>45777</v>
+      </c>
+      <c r="B762" t="n">
+        <v>99.86038000000001</v>
+      </c>
+      <c r="C762" t="n">
+        <v>99.86242666666668</v>
+      </c>
+      <c r="D762" t="n">
+        <v>100.08916</v>
+      </c>
+      <c r="E762" t="n">
+        <v>0.1607406032449346</v>
+      </c>
+      <c r="F762" t="b">
+        <v>1</v>
+      </c>
+      <c r="G762" t="n">
+        <v>0.04018897446938442</v>
+      </c>
+      <c r="H762" t="b">
         <v>0</v>
       </c>
     </row>
